--- a/resources/data-imports/Monsters/ice-plane-raid-monsters.xlsx
+++ b/resources/data-imports/Monsters/ice-plane-raid-monsters.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -372,16 +372,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -405,34 +409,34 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -578,2127 +582,2127 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AX15"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="37.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="21.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="10.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="27" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="0" width="20.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="18.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="24.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="27.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="0" width="20.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="0" width="25.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="0" width="24.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="0" width="16.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="0" width="15.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="0" width="17.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="0" width="14.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="0" width="26.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="0" width="24.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="37.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="14.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="21.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="10.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="6.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="12.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="13.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="1" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="27" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="29" min="29" style="1" width="20.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="1" width="18.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="1" width="24.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="1" width="27.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="1" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="38" min="38" style="1" width="20.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="39" style="1" width="25.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="24.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="41" min="41" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="43" min="42" style="1" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="44" min="44" style="1" width="15.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="46" min="45" style="1" width="17.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="47" min="47" style="1" width="14.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="49" min="48" style="1" width="26.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="50" min="50" style="1" width="24.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AL1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AM1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AN1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AO1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AP1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AR1" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AS1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AT1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AU1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AV1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AW1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AX1" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>561</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="N2" s="0" t="n">
+      <c r="N2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="P2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="0" t="n">
+      <c r="P2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T2" s="0" t="s">
+      <c r="T2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>101.203844091019</v>
       </c>
-      <c r="V2" s="0" t="n">
+      <c r="V2" s="1" t="n">
         <v>0.132600065950184</v>
       </c>
-      <c r="W2" s="0" t="n">
-        <v>3452361601.928</v>
-      </c>
-      <c r="X2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" s="0" t="s">
+      <c r="W2" s="1" t="n">
+        <v>500000</v>
+      </c>
+      <c r="X2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AA2" s="2" t="n">
+      <c r="AA2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="AB2" s="2" t="n">
+      <c r="AB2" s="3" t="n">
         <v>82261873033.9931</v>
       </c>
-      <c r="AC2" s="0" t="n">
+      <c r="AC2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="AD2" s="0" t="n">
+      <c r="AD2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="AE2" s="0" t="n">
+      <c r="AE2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="AF2" s="0" t="n">
+      <c r="AF2" s="1" t="n">
         <v>0.567374148232575</v>
       </c>
-      <c r="AG2" s="0" t="n">
+      <c r="AG2" s="1" t="n">
         <v>0.36336243916928</v>
       </c>
-      <c r="AH2" s="0" t="n">
+      <c r="AH2" s="1" t="n">
         <v>0.36336243916928</v>
       </c>
-      <c r="AI2" s="0" t="n">
+      <c r="AI2" s="1" t="n">
         <v>0.323653746390419</v>
       </c>
-      <c r="AJ2" s="0" t="n">
+      <c r="AJ2" s="1" t="n">
         <v>0.323653746390419</v>
       </c>
-      <c r="AK2" s="0" t="n">
+      <c r="AK2" s="1" t="n">
         <v>0.323653746390419</v>
       </c>
-      <c r="AL2" s="0" t="n">
+      <c r="AL2" s="1" t="n">
         <v>0.323653746390419</v>
       </c>
-      <c r="AM2" s="0" t="s">
+      <c r="AM2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AN2" s="0" t="n">
+      <c r="AN2" s="1" t="n">
         <v>0.05</v>
       </c>
-      <c r="AO2" s="0" t="s">
+      <c r="AO2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ2" s="0" t="n">
+      <c r="AQ2" s="1" t="n">
         <v>0.03980123224752</v>
       </c>
-      <c r="AR2" s="0" t="n">
+      <c r="AR2" s="1" t="n">
         <v>0.03133400638082</v>
       </c>
-      <c r="AS2" s="0" t="n">
+      <c r="AS2" s="1" t="n">
         <v>0.0157379960543689</v>
       </c>
-      <c r="AT2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" s="0" t="n">
+      <c r="AT2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" s="1" t="n">
         <v>0.25908403382488</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>560</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="E3" s="2" t="n">
+      <c r="E3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="K3" s="0" t="n">
+      <c r="K3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="P3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" s="0" t="n">
+      <c r="P3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T3" s="0" t="s">
+      <c r="T3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U3" s="2" t="n">
+      <c r="U3" s="3" t="n">
         <v>115.278472180714</v>
       </c>
-      <c r="V3" s="0" t="n">
+      <c r="V3" s="1" t="n">
         <v>0.152691763195023</v>
       </c>
-      <c r="W3" s="0" t="n">
-        <v>4535857671.80029</v>
-      </c>
-      <c r="X3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" s="0" t="s">
+      <c r="W3" s="1" t="n">
+        <v>693267</v>
+      </c>
+      <c r="X3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="AA3" s="2" t="n">
+      <c r="AA3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="AB3" s="2" t="n">
+      <c r="AB3" s="3" t="n">
         <v>86152375928.6876</v>
       </c>
-      <c r="AC3" s="0" t="n">
+      <c r="AC3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="AD3" s="0" t="n">
+      <c r="AD3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="AE3" s="0" t="n">
+      <c r="AE3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="AF3" s="0" t="n">
+      <c r="AF3" s="1" t="n">
         <v>0.592655943115915</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>0.387199741903663</v>
       </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AH3" s="1" t="n">
         <v>0.387199741903663</v>
       </c>
-      <c r="AI3" s="0" t="n">
+      <c r="AI3" s="1" t="n">
         <v>0.347970111279728</v>
       </c>
-      <c r="AJ3" s="0" t="n">
+      <c r="AJ3" s="1" t="n">
         <v>0.347970111279728</v>
       </c>
-      <c r="AK3" s="0" t="n">
+      <c r="AK3" s="1" t="n">
         <v>0.347970111279728</v>
       </c>
-      <c r="AL3" s="0" t="n">
+      <c r="AL3" s="1" t="n">
         <v>0.347970111279728</v>
       </c>
-      <c r="AM3" s="0" t="s">
+      <c r="AM3" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="0" t="n">
+      <c r="AN3" s="1" t="n">
         <v>0.15</v>
       </c>
-      <c r="AO3" s="0" t="s">
+      <c r="AO3" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ3" s="0" t="n">
+      <c r="AQ3" s="1" t="n">
         <v>0.0458441737371965</v>
       </c>
-      <c r="AR3" s="0" t="n">
+      <c r="AR3" s="1" t="n">
         <v>0.0392201177727384</v>
       </c>
-      <c r="AS3" s="0" t="n">
+      <c r="AS3" s="1" t="n">
         <v>0.0197435001847596</v>
       </c>
-      <c r="AT3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" s="0" t="n">
+      <c r="AT3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="1" t="n">
         <v>0.281157475338692</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>559</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="K4" s="0" t="n">
+      <c r="K4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="P4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="0" t="n">
+      <c r="P4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T4" s="0" t="s">
+      <c r="T4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U4" s="2" t="n">
+      <c r="U4" s="3" t="n">
         <v>131.310487933323</v>
       </c>
-      <c r="V4" s="0" t="n">
+      <c r="V4" s="1" t="n">
         <v>0.175827774899932</v>
       </c>
-      <c r="W4" s="0" t="n">
-        <v>5959400315.23343</v>
-      </c>
-      <c r="X4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="0" t="s">
+      <c r="W4" s="1" t="n">
+        <v>961239</v>
+      </c>
+      <c r="X4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Z4" s="0" t="s">
+      <c r="Z4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AA4" s="2" t="n">
+      <c r="AA4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="AB4" s="2" t="n">
+      <c r="AB4" s="3" t="n">
         <v>90226876734.144</v>
       </c>
-      <c r="AC4" s="0" t="n">
+      <c r="AC4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="AD4" s="0" t="n">
+      <c r="AD4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="AE4" s="0" t="n">
+      <c r="AE4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="AF4" s="0" t="n">
+      <c r="AF4" s="1" t="n">
         <v>0.619064277082</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>0.412600819372027</v>
       </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AH4" s="1" t="n">
         <v>0.412600819372027</v>
       </c>
-      <c r="AI4" s="0" t="n">
+      <c r="AI4" s="1" t="n">
         <v>0.374113384116264</v>
       </c>
-      <c r="AJ4" s="0" t="n">
+      <c r="AJ4" s="1" t="n">
         <v>0.374113384116264</v>
       </c>
-      <c r="AK4" s="0" t="n">
+      <c r="AK4" s="1" t="n">
         <v>0.374113384116264</v>
       </c>
-      <c r="AL4" s="0" t="n">
+      <c r="AL4" s="1" t="n">
         <v>0.374113384116264</v>
       </c>
-      <c r="AM4" s="0" t="s">
+      <c r="AM4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="AN4" s="0" t="n">
+      <c r="AN4" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="AO4" s="0" t="s">
+      <c r="AO4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ4" s="0" t="n">
+      <c r="AQ4" s="1" t="n">
         <v>0.0528046029473675</v>
       </c>
-      <c r="AR4" s="0" t="n">
+      <c r="AR4" s="1" t="n">
         <v>0.0490909977936634</v>
       </c>
-      <c r="AS4" s="0" t="n">
+      <c r="AS4" s="1" t="n">
         <v>0.0247684519807331</v>
       </c>
-      <c r="AT4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" s="0" t="n">
+      <c r="AT4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="1" t="n">
         <v>0.305111529922598</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>558</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="H5" s="2" t="n">
+      <c r="H5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="J5" s="2" t="n">
+      <c r="J5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="K5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="P5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S5" s="0" t="n">
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T5" s="0" t="s">
+      <c r="T5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U5" s="2" t="n">
+      <c r="U5" s="3" t="n">
         <v>149.57210930292</v>
       </c>
-      <c r="V5" s="0" t="n">
+      <c r="V5" s="1" t="n">
         <v>0.2024693786971</v>
       </c>
-      <c r="W5" s="0" t="n">
-        <v>7829710428.96692</v>
-      </c>
-      <c r="X5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="0" t="s">
+      <c r="W5" s="1" t="n">
+        <v>1332790</v>
+      </c>
+      <c r="X5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="AA5" s="2" t="n">
+      <c r="AA5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="AB5" s="2" t="n">
+      <c r="AB5" s="3" t="n">
         <v>94494077469.6338</v>
       </c>
-      <c r="AC5" s="0" t="n">
+      <c r="AC5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="AD5" s="0" t="n">
+      <c r="AD5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="AE5" s="0" t="n">
+      <c r="AE5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="AF5" s="0" t="n">
+      <c r="AF5" s="1" t="n">
         <v>0.64664934792378</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AG5" s="1" t="n">
         <v>0.439668258324471</v>
       </c>
-      <c r="AH5" s="0" t="n">
+      <c r="AH5" s="1" t="n">
         <v>0.439668258324471</v>
       </c>
-      <c r="AI5" s="0" t="n">
+      <c r="AI5" s="1" t="n">
         <v>0.402220821955626</v>
       </c>
-      <c r="AJ5" s="0" t="n">
+      <c r="AJ5" s="1" t="n">
         <v>0.402220821955626</v>
       </c>
-      <c r="AK5" s="0" t="n">
+      <c r="AK5" s="1" t="n">
         <v>0.402220821955626</v>
       </c>
-      <c r="AL5" s="0" t="n">
+      <c r="AL5" s="1" t="n">
         <v>0.402220821955626</v>
       </c>
-      <c r="AN5" s="0" t="n">
+      <c r="AN5" s="1" t="n">
         <v>0.58</v>
       </c>
-      <c r="AO5" s="0" t="s">
+      <c r="AO5" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ5" s="0" t="n">
+      <c r="AQ5" s="1" t="n">
         <v>0.0608218202036605</v>
       </c>
-      <c r="AR5" s="0" t="n">
+      <c r="AR5" s="1" t="n">
         <v>0.0614461710273748</v>
       </c>
-      <c r="AS5" s="0" t="n">
+      <c r="AS5" s="1" t="n">
         <v>0.0310723128007178</v>
       </c>
-      <c r="AT5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" s="0" t="n">
+      <c r="AT5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" s="1" t="n">
         <v>0.331106422048944</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>557</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="E6" s="2" t="n">
+      <c r="E6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="H6" s="2" t="n">
+      <c r="H6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="K6" s="0" t="n">
+      <c r="K6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="P6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="0" t="n">
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T6" s="0" t="s">
+      <c r="T6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U6" s="2" t="n">
+      <c r="U6" s="3" t="n">
         <v>170.373412157944</v>
       </c>
-      <c r="V6" s="0" t="n">
+      <c r="V6" s="1" t="n">
         <v>0.23314774547605</v>
       </c>
-      <c r="W6" s="0" t="n">
-        <v>10287002409.4148</v>
-      </c>
-      <c r="X6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="0" t="s">
+      <c r="W6" s="1" t="n">
+        <v>1847960</v>
+      </c>
+      <c r="X6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="Z6" s="0" t="s">
+      <c r="Z6" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="AA6" s="2" t="n">
+      <c r="AA6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="AB6" s="2" t="n">
+      <c r="AB6" s="3" t="n">
         <v>98963091708.772</v>
       </c>
-      <c r="AC6" s="0" t="n">
+      <c r="AC6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="AD6" s="0" t="n">
+      <c r="AD6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="AE6" s="0" t="n">
+      <c r="AE6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="AF6" s="0" t="n">
+      <c r="AF6" s="1" t="n">
         <v>0.675463590212719</v>
       </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
         <v>0.468511375407073</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AH6" s="1" t="n">
         <v>0.468511375407073</v>
       </c>
-      <c r="AI6" s="0" t="n">
+      <c r="AI6" s="1" t="n">
         <v>0.432439994085809</v>
       </c>
-      <c r="AJ6" s="0" t="n">
+      <c r="AJ6" s="1" t="n">
         <v>0.432439994085809</v>
       </c>
-      <c r="AK6" s="0" t="n">
+      <c r="AK6" s="1" t="n">
         <v>0.432439994085809</v>
       </c>
-      <c r="AL6" s="0" t="n">
+      <c r="AL6" s="1" t="n">
         <v>0.432439994085809</v>
       </c>
-      <c r="AO6" s="0" t="s">
+      <c r="AO6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ6" s="0" t="n">
+      <c r="AQ6" s="1" t="n">
         <v>0.0700562755215418</v>
       </c>
-      <c r="AR6" s="0" t="n">
+      <c r="AR6" s="1" t="n">
         <v>0.0769108819053735</v>
       </c>
-      <c r="AS6" s="0" t="n">
+      <c r="AS6" s="1" t="n">
         <v>0.0389805799545603</v>
       </c>
-      <c r="AT6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" s="0" t="n">
+      <c r="AT6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" s="1" t="n">
         <v>0.35931602699467</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>556</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="H7" s="2" t="n">
+      <c r="H7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="J7" s="2" t="n">
+      <c r="J7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="K7" s="0" t="n">
+      <c r="K7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="P7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" s="0" t="n">
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T7" s="0" t="s">
+      <c r="T7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U7" s="2" t="n">
+      <c r="U7" s="3" t="n">
         <v>194.067595259712</v>
       </c>
-      <c r="V7" s="0" t="n">
+      <c r="V7" s="1" t="n">
         <v>0.268474529681282</v>
       </c>
-      <c r="W7" s="0" t="n">
-        <v>13515495819.5903</v>
-      </c>
-      <c r="X7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="0" t="s">
+      <c r="W7" s="1" t="n">
+        <v>2562259</v>
+      </c>
+      <c r="X7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="AA7" s="2" t="n">
+      <c r="AA7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="AB7" s="2" t="n">
+      <c r="AB7" s="3" t="n">
         <v>103643464043.618</v>
       </c>
-      <c r="AC7" s="0" t="n">
+      <c r="AC7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="AD7" s="0" t="n">
+      <c r="AD7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="AE7" s="0" t="n">
+      <c r="AE7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="AF7" s="0" t="n">
+      <c r="AF7" s="1" t="n">
         <v>0.705561774968085</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>0.499246658656528</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AH7" s="1" t="n">
         <v>0.499246658656528</v>
       </c>
-      <c r="AI7" s="0" t="n">
+      <c r="AI7" s="1" t="n">
         <v>0.464929556793471</v>
       </c>
-      <c r="AJ7" s="0" t="n">
+      <c r="AJ7" s="1" t="n">
         <v>0.464929556793471</v>
       </c>
-      <c r="AK7" s="0" t="n">
+      <c r="AK7" s="1" t="n">
         <v>0.464929556793471</v>
       </c>
-      <c r="AL7" s="0" t="n">
+      <c r="AL7" s="1" t="n">
         <v>0.464929556793471</v>
       </c>
-      <c r="AM7" s="0" t="s">
+      <c r="AM7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AN7" s="0" t="n">
+      <c r="AN7" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="AO7" s="0" t="s">
+      <c r="AO7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ7" s="0" t="n">
+      <c r="AQ7" s="1" t="n">
         <v>0.0806927797214265</v>
       </c>
-      <c r="AR7" s="0" t="n">
+      <c r="AR7" s="1" t="n">
         <v>0.096267735752436</v>
       </c>
-      <c r="AS7" s="0" t="n">
+      <c r="AS7" s="1" t="n">
         <v>0.0489015936257814</v>
       </c>
-      <c r="AT7" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" s="0" t="n">
+      <c r="AT7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" s="1" t="n">
         <v>0.389929033862562</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>555</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="E8" s="2" t="n">
+      <c r="E8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="H8" s="2" t="n">
+      <c r="H8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="J8" s="2" t="n">
+      <c r="J8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="K8" s="0" t="n">
+      <c r="K8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="P8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="0" t="n">
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T8" s="0" t="s">
+      <c r="T8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U8" s="2" t="n">
+      <c r="U8" s="3" t="n">
         <v>221.056977452403</v>
       </c>
-      <c r="V8" s="0" t="n">
+      <c r="V8" s="1" t="n">
         <v>0.30915406426261</v>
       </c>
-      <c r="W8" s="0" t="n">
-        <v>17757226058.6022</v>
-      </c>
-      <c r="X8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="0" t="s">
+      <c r="W8" s="1" t="n">
+        <v>3552661</v>
+      </c>
+      <c r="X8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="Z8" s="0" t="s">
+      <c r="Z8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AA8" s="2" t="n">
+      <c r="AA8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="AB8" s="2" t="n">
+      <c r="AB8" s="3" t="n">
         <v>108545190469.312</v>
       </c>
-      <c r="AC8" s="0" t="n">
+      <c r="AC8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="AD8" s="0" t="n">
+      <c r="AD8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="AE8" s="0" t="n">
+      <c r="AE8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="AF8" s="0" t="n">
+      <c r="AF8" s="1" t="n">
         <v>0.73700111376742</v>
       </c>
-      <c r="AG8" s="0" t="n">
+      <c r="AG8" s="1" t="n">
         <v>0.531998237957713</v>
       </c>
-      <c r="AH8" s="0" t="n">
+      <c r="AH8" s="1" t="n">
         <v>0.531998237957713</v>
       </c>
-      <c r="AI8" s="0" t="n">
+      <c r="AI8" s="1" t="n">
         <v>0.49986008633901</v>
       </c>
-      <c r="AJ8" s="0" t="n">
+      <c r="AJ8" s="1" t="n">
         <v>0.49986008633901</v>
       </c>
-      <c r="AK8" s="0" t="n">
+      <c r="AK8" s="1" t="n">
         <v>0.49986008633901</v>
       </c>
-      <c r="AL8" s="0" t="n">
+      <c r="AL8" s="1" t="n">
         <v>0.49986008633901</v>
       </c>
-      <c r="AN8" s="0" t="n">
+      <c r="AN8" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="AO8" s="0" t="s">
+      <c r="AO8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ8" s="0" t="n">
+      <c r="AQ8" s="1" t="n">
         <v>0.0929442030809712</v>
       </c>
-      <c r="AR8" s="0" t="n">
+      <c r="AR8" s="1" t="n">
         <v>0.120496303218873</v>
       </c>
-      <c r="AS8" s="0" t="n">
+      <c r="AS8" s="1" t="n">
         <v>0.0613476213521881</v>
       </c>
-      <c r="AT8" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" s="0" t="n">
+      <c r="AT8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="1" t="n">
         <v>0.423150207689584</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>424</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="E9" s="2" t="n">
+      <c r="E9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="H9" s="2" t="n">
+      <c r="H9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="J9" s="2" t="n">
+      <c r="J9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="K9" s="0" t="n">
+      <c r="K9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="P9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" s="0" t="n">
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T9" s="0" t="s">
+      <c r="T9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="U9" s="2" t="n">
+      <c r="U9" s="3" t="n">
         <v>251.799828894652</v>
       </c>
-      <c r="V9" s="0" t="n">
+      <c r="V9" s="1" t="n">
         <v>0.355997403416826</v>
       </c>
-      <c r="W9" s="0" t="n">
-        <v>23330189399.286</v>
-      </c>
-      <c r="X9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="0" t="s">
+      <c r="W9" s="1" t="n">
+        <v>4925886</v>
+      </c>
+      <c r="X9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="Z9" s="0" t="s">
+      <c r="Z9" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="AA9" s="2" t="n">
+      <c r="AA9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="AB9" s="2" t="n">
+      <c r="AB9" s="3" t="n">
         <v>113678739732.791</v>
       </c>
-      <c r="AC9" s="0" t="n">
+      <c r="AC9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="AD9" s="0" t="n">
+      <c r="AD9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="AE9" s="0" t="n">
+      <c r="AE9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="AF9" s="0" t="n">
+      <c r="AF9" s="1" t="n">
         <v>0.769841367496117</v>
       </c>
-      <c r="AG9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
         <v>0.566898386364215</v>
       </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AH9" s="1" t="n">
         <v>0.566898386364215</v>
       </c>
-      <c r="AI9" s="0" t="n">
+      <c r="AI9" s="1" t="n">
         <v>0.537414974513729</v>
       </c>
-      <c r="AJ9" s="0" t="n">
+      <c r="AJ9" s="1" t="n">
         <v>0.537414974513729</v>
       </c>
-      <c r="AK9" s="0" t="n">
+      <c r="AK9" s="1" t="n">
         <v>0.537414974513729</v>
       </c>
-      <c r="AL9" s="0" t="n">
+      <c r="AL9" s="1" t="n">
         <v>0.537414974513729</v>
       </c>
-      <c r="AO9" s="0" t="s">
+      <c r="AO9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ9" s="0" t="n">
+      <c r="AQ9" s="1" t="n">
         <v>0.107055735546349</v>
       </c>
-      <c r="AR9" s="0" t="n">
+      <c r="AR9" s="1" t="n">
         <v>0.150822692316696</v>
       </c>
-      <c r="AS9" s="0" t="n">
+      <c r="AS9" s="1" t="n">
         <v>0.0769613087534898</v>
       </c>
-      <c r="AT9" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" s="0" t="n">
+      <c r="AT9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" s="1" t="n">
         <v>0.459201759084321</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>423</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="H10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="J10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="K10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="P10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" s="0" t="n">
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T10" s="0" t="s">
+      <c r="T10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="U10" s="2" t="n">
+      <c r="U10" s="3" t="n">
         <v>286.818152324677</v>
       </c>
-      <c r="V10" s="0" t="n">
+      <c r="V10" s="1" t="n">
         <v>0.409938493099895</v>
       </c>
-      <c r="W10" s="0" t="n">
-        <v>30652182700.7367</v>
-      </c>
-      <c r="X10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" s="0" t="s">
+      <c r="W10" s="1" t="n">
+        <v>6829909</v>
+      </c>
+      <c r="X10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Z10" s="0" t="s">
+      <c r="Z10" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="AA10" s="2" t="n">
+      <c r="AA10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="AB10" s="2" t="n">
+      <c r="AB10" s="3" t="n">
         <v>119055075691.162</v>
       </c>
-      <c r="AC10" s="0" t="n">
+      <c r="AC10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="AD10" s="0" t="n">
+      <c r="AD10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="AE10" s="0" t="n">
+      <c r="AE10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="AF10" s="0" t="n">
+      <c r="AF10" s="1" t="n">
         <v>0.804144959942787</v>
       </c>
-      <c r="AG10" s="0" t="n">
+      <c r="AG10" s="1" t="n">
         <v>0.60408805430648</v>
       </c>
-      <c r="AH10" s="0" t="n">
+      <c r="AH10" s="1" t="n">
         <v>0.60408805430648</v>
       </c>
-      <c r="AI10" s="0" t="n">
+      <c r="AI10" s="1" t="n">
         <v>0.577791391480925</v>
       </c>
-      <c r="AJ10" s="0" t="n">
+      <c r="AJ10" s="1" t="n">
         <v>0.577791391480925</v>
       </c>
-      <c r="AK10" s="0" t="n">
+      <c r="AK10" s="1" t="n">
         <v>0.577791391480925</v>
       </c>
-      <c r="AL10" s="0" t="n">
+      <c r="AL10" s="1" t="n">
         <v>0.577791391480925</v>
       </c>
-      <c r="AO10" s="0" t="s">
+      <c r="AO10" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ10" s="0" t="n">
+      <c r="AQ10" s="1" t="n">
         <v>0.12330979376288</v>
       </c>
-      <c r="AR10" s="0" t="n">
+      <c r="AR10" s="1" t="n">
         <v>0.18878159669627</v>
       </c>
-      <c r="AS10" s="0" t="n">
+      <c r="AS10" s="1" t="n">
         <v>0.0965488622785654</v>
       </c>
-      <c r="AT10" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" s="0" t="n">
+      <c r="AT10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" s="1" t="n">
         <v>0.498324830554787</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>422</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="2" t="n">
+      <c r="C11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="E11" s="2" t="n">
+      <c r="E11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="H11" s="2" t="n">
+      <c r="H11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="I11" s="2" t="n">
+      <c r="I11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="J11" s="2" t="n">
+      <c r="J11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="K11" s="0" t="n">
+      <c r="K11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="P11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="0" t="n">
+      <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T11" s="0" t="s">
+      <c r="T11" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U11" s="2" t="n">
+      <c r="U11" s="3" t="n">
         <v>326.706546482045</v>
       </c>
-      <c r="V11" s="0" t="n">
+      <c r="V11" s="1" t="n">
         <v>0.472052791711654</v>
       </c>
-      <c r="W11" s="0" t="n">
-        <v>40272125023.9013</v>
-      </c>
-      <c r="X11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="0" t="s">
+      <c r="W11" s="1" t="n">
+        <v>9469904</v>
+      </c>
+      <c r="X11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Z11" s="0" t="s">
+      <c r="Z11" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="AA11" s="2" t="n">
+      <c r="AA11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="AB11" s="2" t="n">
+      <c r="AB11" s="3" t="n">
         <v>124685680727.509</v>
       </c>
-      <c r="AC11" s="0" t="n">
+      <c r="AC11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="AD11" s="0" t="n">
+      <c r="AD11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="AE11" s="0" t="n">
+      <c r="AE11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="AF11" s="0" t="n">
+      <c r="AF11" s="1" t="n">
         <v>0.839977096456365</v>
       </c>
-      <c r="AG11" s="0" t="n">
+      <c r="AG11" s="1" t="n">
         <v>0.643717438845094</v>
       </c>
-      <c r="AH11" s="0" t="n">
+      <c r="AH11" s="1" t="n">
         <v>0.643717438845094</v>
       </c>
-      <c r="AI11" s="0" t="n">
+      <c r="AI11" s="1" t="n">
         <v>0.621201320956</v>
       </c>
-      <c r="AJ11" s="0" t="n">
+      <c r="AJ11" s="1" t="n">
         <v>0.621201320956</v>
       </c>
-      <c r="AK11" s="0" t="n">
+      <c r="AK11" s="1" t="n">
         <v>0.621201320956</v>
       </c>
-      <c r="AL11" s="0" t="n">
+      <c r="AL11" s="1" t="n">
         <v>0.621201320956</v>
       </c>
-      <c r="AM11" s="0" t="s">
+      <c r="AM11" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AN11" s="0" t="n">
+      <c r="AN11" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="AO11" s="0" t="s">
+      <c r="AO11" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ11" s="0" t="n">
+      <c r="AQ11" s="1" t="n">
         <v>0.142031673130311</v>
       </c>
-      <c r="AR11" s="0" t="n">
+      <c r="AR11" s="1" t="n">
         <v>0.23629396017119</v>
       </c>
-      <c r="AS11" s="0" t="n">
+      <c r="AS11" s="1" t="n">
         <v>0.121121677350149</v>
       </c>
-      <c r="AT11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" s="0" t="n">
+      <c r="AT11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" s="1" t="n">
         <v>0.540781109468394</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>421</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C12" s="2" t="n">
+      <c r="C12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="E12" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="H12" s="2" t="n">
+      <c r="H12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="I12" s="2" t="n">
+      <c r="I12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="J12" s="2" t="n">
+      <c r="J12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="K12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="P12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" s="0" t="n">
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T12" s="0" t="s">
+      <c r="T12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U12" s="2" t="n">
+      <c r="U12" s="3" t="n">
         <v>372.142302183854</v>
       </c>
-      <c r="V12" s="0" t="n">
+      <c r="V12" s="1" t="n">
         <v>0.543578712205651</v>
       </c>
-      <c r="W12" s="0" t="n">
-        <v>52911209285.6525</v>
-      </c>
-      <c r="X12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="0" t="s">
+      <c r="W12" s="1" t="n">
+        <v>13130346</v>
+      </c>
+      <c r="X12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="Z12" s="0" t="s">
+      <c r="Z12" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="AA12" s="2" t="n">
+      <c r="AA12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="AB12" s="2" t="n">
+      <c r="AB12" s="3" t="n">
         <v>130582580274.118</v>
       </c>
-      <c r="AC12" s="0" t="n">
+      <c r="AC12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="AD12" s="0" t="n">
+      <c r="AD12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="AE12" s="0" t="n">
+      <c r="AE12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="AF12" s="0" t="n">
+      <c r="AF12" s="1" t="n">
         <v>0.877405887890494</v>
       </c>
-      <c r="AG12" s="0" t="n">
+      <c r="AG12" s="1" t="n">
         <v>0.68594659026821</v>
       </c>
-      <c r="AH12" s="0" t="n">
+      <c r="AH12" s="1" t="n">
         <v>0.68594659026821</v>
       </c>
-      <c r="AI12" s="0" t="n">
+      <c r="AI12" s="1" t="n">
         <v>0.667872673160481</v>
       </c>
-      <c r="AJ12" s="0" t="n">
+      <c r="AJ12" s="1" t="n">
         <v>0.667872673160481</v>
       </c>
-      <c r="AK12" s="0" t="n">
+      <c r="AK12" s="1" t="n">
         <v>0.667872673160481</v>
       </c>
-      <c r="AL12" s="0" t="n">
+      <c r="AL12" s="1" t="n">
         <v>0.667872673160481</v>
       </c>
-      <c r="AM12" s="0" t="s">
+      <c r="AM12" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AN12" s="0" t="n">
+      <c r="AN12" s="1" t="n">
         <v>0.58</v>
       </c>
-      <c r="AO12" s="0" t="s">
+      <c r="AO12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ12" s="0" t="n">
+      <c r="AQ12" s="1" t="n">
         <v>0.163596057998339</v>
       </c>
-      <c r="AR12" s="0" t="n">
+      <c r="AR12" s="1" t="n">
         <v>0.295764187773116</v>
       </c>
-      <c r="AS12" s="0" t="n">
+      <c r="AS12" s="1" t="n">
         <v>0.151948561359387</v>
       </c>
-      <c r="AT12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" s="0" t="n">
+      <c r="AT12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" s="1" t="n">
         <v>0.586854578432883</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>420</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C13" s="2" t="n">
+      <c r="C13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="E13" s="2" t="n">
+      <c r="E13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="H13" s="2" t="n">
+      <c r="H13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="I13" s="2" t="n">
+      <c r="I13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="J13" s="2" t="n">
+      <c r="J13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="P13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" s="0" t="n">
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T13" s="0" t="s">
+      <c r="T13" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U13" s="2" t="n">
+      <c r="U13" s="3" t="n">
         <v>423.896902483128</v>
       </c>
-      <c r="V13" s="0" t="n">
+      <c r="V13" s="1" t="n">
         <v>0.625942313129338</v>
       </c>
-      <c r="W13" s="0" t="n">
-        <v>69516969030.2803</v>
-      </c>
-      <c r="X13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="0" t="s">
+      <c r="W13" s="1" t="n">
+        <v>18205676</v>
+      </c>
+      <c r="X13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Z13" s="0" t="s">
+      <c r="Z13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="AA13" s="2" t="n">
+      <c r="AA13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="AB13" s="2" t="n">
+      <c r="AB13" s="3" t="n">
         <v>136758368495.511</v>
       </c>
-      <c r="AC13" s="0" t="n">
+      <c r="AC13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="AD13" s="0" t="n">
+      <c r="AD13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="AE13" s="0" t="n">
+      <c r="AE13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="AF13" s="0" t="n">
+      <c r="AF13" s="1" t="n">
         <v>0.916502480070772</v>
       </c>
-      <c r="AG13" s="0" t="n">
+      <c r="AG13" s="1" t="n">
         <v>0.730946058482984</v>
       </c>
-      <c r="AH13" s="0" t="n">
+      <c r="AH13" s="1" t="n">
         <v>0.730946058482984</v>
       </c>
-      <c r="AI13" s="0" t="n">
+      <c r="AI13" s="1" t="n">
         <v>0.718050481393167</v>
       </c>
-      <c r="AJ13" s="0" t="n">
+      <c r="AJ13" s="1" t="n">
         <v>0.718050481393167</v>
       </c>
-      <c r="AK13" s="0" t="n">
+      <c r="AK13" s="1" t="n">
         <v>0.718050481393167</v>
       </c>
-      <c r="AL13" s="0" t="n">
+      <c r="AL13" s="1" t="n">
         <v>0.718050481393167</v>
       </c>
-      <c r="AM13" s="0" t="s">
+      <c r="AM13" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AN13" s="0" t="n">
+      <c r="AN13" s="1" t="n">
         <v>0.25</v>
       </c>
-      <c r="AO13" s="0" t="s">
+      <c r="AO13" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ13" s="0" t="n">
+      <c r="AQ13" s="1" t="n">
         <v>0.188434520292111</v>
       </c>
-      <c r="AR13" s="0" t="n">
+      <c r="AR13" s="1" t="n">
         <v>0.370201822787665</v>
       </c>
-      <c r="AS13" s="0" t="n">
+      <c r="AS13" s="1" t="n">
         <v>0.190621248023519</v>
       </c>
-      <c r="AT13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" s="0" t="n">
+      <c r="AT13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" s="1" t="n">
         <v>0.636853414806207</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>419</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="2" t="n">
+      <c r="C14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="D14" s="2" t="n">
+      <c r="D14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="H14" s="2" t="n">
+      <c r="H14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="I14" s="2" t="n">
+      <c r="I14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="J14" s="2" t="n">
+      <c r="J14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="K14" s="0" t="n">
+      <c r="K14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="P14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="0" t="n">
+      <c r="P14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S14" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T14" s="0" t="s">
+      <c r="T14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="U14" s="2" t="n">
+      <c r="U14" s="3" t="n">
         <v>482.849122178045</v>
       </c>
-      <c r="V14" s="0" t="n">
+      <c r="V14" s="1" t="n">
         <v>0.720785730875855</v>
       </c>
-      <c r="W14" s="0" t="n">
-        <v>91334313624.6815</v>
-      </c>
-      <c r="X14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="0" t="s">
+      <c r="W14" s="1" t="n">
+        <v>25242794</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="Z14" s="0" t="s">
+      <c r="Z14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AA14" s="2" t="n">
+      <c r="AA14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="AB14" s="2" t="n">
+      <c r="AB14" s="3" t="n">
         <v>143226235186.142</v>
       </c>
-      <c r="AC14" s="0" t="n">
+      <c r="AC14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="AD14" s="0" t="n">
+      <c r="AD14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="AE14" s="0" t="n">
+      <c r="AE14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="AF14" s="0" t="n">
+      <c r="AF14" s="1" t="n">
         <v>0.95734118903099</v>
       </c>
-      <c r="AG14" s="0" t="n">
+      <c r="AG14" s="1" t="n">
         <v>0.778897581811585</v>
       </c>
-      <c r="AH14" s="0" t="n">
+      <c r="AH14" s="1" t="n">
         <v>0.778897581811585</v>
       </c>
-      <c r="AI14" s="0" t="n">
+      <c r="AI14" s="1" t="n">
         <v>0.771998188500621</v>
       </c>
-      <c r="AJ14" s="0" t="n">
+      <c r="AJ14" s="1" t="n">
         <v>0.771998188500621</v>
       </c>
-      <c r="AK14" s="0" t="n">
+      <c r="AK14" s="1" t="n">
         <v>0.771998188500621</v>
       </c>
-      <c r="AL14" s="0" t="n">
+      <c r="AL14" s="1" t="n">
         <v>0.771998188500621</v>
       </c>
-      <c r="AM14" s="0" t="s">
+      <c r="AM14" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AN14" s="0" t="n">
+      <c r="AN14" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="AO14" s="0" t="s">
+      <c r="AO14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ14" s="0" t="n">
+      <c r="AQ14" s="1" t="n">
         <v>0.217044156639022</v>
       </c>
-      <c r="AR14" s="0" t="n">
+      <c r="AR14" s="1" t="n">
         <v>0.463373847345042</v>
       </c>
-      <c r="AS14" s="0" t="n">
+      <c r="AS14" s="1" t="n">
         <v>0.239136585914106</v>
       </c>
-      <c r="AT14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" s="0" t="n">
+      <c r="AT14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" s="1" t="n">
         <v>0.691112052040867</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>418</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="2" t="n">
+      <c r="C15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="D15" s="2" t="n">
+      <c r="D15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="E15" s="2" t="n">
+      <c r="E15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="H15" s="2" t="n">
+      <c r="H15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="I15" s="2" t="n">
+      <c r="I15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="J15" s="2" t="n">
+      <c r="J15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="K15" s="0" t="n">
+      <c r="K15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="P15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="0" t="n">
+      <c r="P15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S15" s="1" t="n">
         <v>5001</v>
       </c>
-      <c r="T15" s="0" t="s">
+      <c r="T15" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="U15" s="2" t="n">
+      <c r="U15" s="3" t="n">
         <v>549.999949097029</v>
       </c>
-      <c r="V15" s="0" t="n">
+      <c r="V15" s="1" t="n">
         <v>0.829999920019609</v>
       </c>
-      <c r="W15" s="0" t="n">
-        <v>119998857281.279</v>
-      </c>
-      <c r="X15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="0" t="s">
+      <c r="W15" s="1" t="n">
+        <v>34999999</v>
+      </c>
+      <c r="X15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="Z15" s="0" t="s">
+      <c r="Z15" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="AA15" s="2" t="n">
+      <c r="AA15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="AB15" s="2" t="n">
+      <c r="AB15" s="3" t="n">
         <v>150000000000</v>
       </c>
-      <c r="AC15" s="0" t="n">
+      <c r="AC15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="AD15" s="0" t="n">
+      <c r="AD15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="AE15" s="0" t="n">
+      <c r="AE15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="AF15" s="0" t="n">
+      <c r="AF15" s="1" t="n">
         <v>0.999999642275378</v>
       </c>
-      <c r="AG15" s="0" t="n">
+      <c r="AG15" s="1" t="n">
         <v>0.829994820973589</v>
       </c>
-      <c r="AH15" s="0" t="n">
+      <c r="AH15" s="1" t="n">
         <v>0.829994820973589</v>
       </c>
-      <c r="AI15" s="0" t="n">
+      <c r="AI15" s="1" t="n">
         <v>0.829999030001223</v>
       </c>
-      <c r="AJ15" s="0" t="n">
+      <c r="AJ15" s="1" t="n">
         <v>0.829999030001223</v>
       </c>
-      <c r="AK15" s="0" t="n">
+      <c r="AK15" s="1" t="n">
         <v>0.829999030001223</v>
       </c>
-      <c r="AL15" s="0" t="n">
+      <c r="AL15" s="1" t="n">
         <v>0.829999030001223</v>
       </c>
-      <c r="AO15" s="0" t="s">
+      <c r="AO15" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="AQ15" s="0" t="n">
+      <c r="AQ15" s="1" t="n">
         <v>0.249997536853211</v>
       </c>
-      <c r="AR15" s="0" t="n">
+      <c r="AR15" s="1" t="n">
         <v>0.579995313870995</v>
       </c>
-      <c r="AS15" s="0" t="n">
+      <c r="AS15" s="1" t="n">
         <v>0.299999644927301</v>
       </c>
-      <c r="AT15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" s="0" t="n">
+      <c r="AT15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" s="1" t="n">
         <v>0.749993416650645</v>
       </c>
     </row>
